--- a/public/file/Trax Book Retail Shipment Template.xlsx
+++ b/public/file/Trax Book Retail Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF19116-361D-4FC5-8A1D-6F1011C555AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEC2D66-89A2-404D-9190-42A38EFA1F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1776" windowWidth="11172" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Consignee CNIC</t>
   </si>
   <si>
-    <t>Insurance Offered</t>
-  </si>
-  <si>
     <t>Weight Charges</t>
   </si>
   <si>
@@ -97,6 +94,15 @@
   </si>
   <si>
     <t>Bank ID</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Trax Box ID</t>
+  </si>
+  <si>
+    <t>Volumetric Weight</t>
   </si>
 </sst>
 </file>
@@ -449,46 +455,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.109375" style="1" customWidth="1"/>
-    <col min="34" max="38" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -499,67 +497,73 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Retail Shipment Template.xlsx
+++ b/public/file/Trax Book Retail Shipment Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEC2D66-89A2-404D-9190-42A38EFA1F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F67543D-6084-4CD6-9DF1-27DC09E3508C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1776" windowWidth="11172" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Volumetric Weight</t>
+  </si>
+  <si>
+    <t>Charges Mode ID</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -469,24 +472,25 @@
     <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="30.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" customWidth="1"/>
+    <col min="13" max="13" width="30.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -521,48 +525,51 @@
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/public/file/Trax Book Retail Shipment Template.xlsx
+++ b/public/file/Trax Book Retail Shipment Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F67543D-6084-4CD6-9DF1-27DC09E3508C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D93E274-396B-4605-9A46-B15FAA52EAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Charges Mode ID</t>
+  </si>
+  <si>
+    <t>Special Instruction</t>
   </si>
 </sst>
 </file>
@@ -458,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -490,7 +493,7 @@
     <col min="27" max="27" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -571,6 +574,9 @@
       </c>
       <c r="AA1" s="1" t="s">
         <v>22</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Retail Shipment Template.xlsx
+++ b/public/file/Trax Book Retail Shipment Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D93E274-396B-4605-9A46-B15FAA52EAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -73,12 +72,6 @@
   </si>
   <si>
     <t>Consignee CNIC</t>
-  </si>
-  <si>
-    <t>Weight Charges</t>
-  </si>
-  <si>
-    <t>Fuel Surcharge</t>
   </si>
   <si>
     <t>IBAN Number</t>
@@ -114,7 +107,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -460,8 +453,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -486,14 +479,12 @@
     <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -504,10 +495,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -528,10 +519,10 @@
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
@@ -543,7 +534,7 @@
         <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>0</v>
@@ -558,7 +549,7 @@
         <v>2</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>16</v>
@@ -567,16 +558,10 @@
         <v>17</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/public/file/Trax Book Retail Shipment Template.xlsx
+++ b/public/file/Trax Book Retail Shipment Template.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -102,16 +102,31 @@
   </si>
   <si>
     <t>Special Instruction</t>
+  </si>
+  <si>
+    <t>Insurance Offered</t>
+  </si>
+  <si>
+    <t>Insurance Value</t>
+  </si>
+  <si>
+    <t>Packaging Charges</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -137,9 +152,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -478,13 +496,14 @@
     <col min="19" max="19" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="14.5546875" style="1" customWidth="1"/>
     <col min="25" max="25" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -549,18 +568,27 @@
         <v>2</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
     </row>

--- a/public/file/Trax Book Retail Shipment Template.xlsx
+++ b/public/file/Trax Book Retail Shipment Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9084FCFB-A219-4F4F-A475-0E31AE8ECD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Consignee Name</t>
   </si>
@@ -111,12 +112,18 @@
   </si>
   <si>
     <t>Packaging Charges</t>
+  </si>
+  <si>
+    <t>Admin Discount Type</t>
+  </si>
+  <si>
+    <t>Admin Discount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -471,8 +478,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -501,9 +508,12 @@
     <col min="26" max="26" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5546875" customWidth="1"/>
+    <col min="30" max="30" width="13.77734375" customWidth="1"/>
+    <col min="31" max="31" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -590,6 +600,12 @@
       </c>
       <c r="AC1" s="1" t="s">
         <v>25</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
